--- a/osce-engine/docs/OSCE_Engine_Analysis.xlsx
+++ b/osce-engine/docs/OSCE_Engine_Analysis.xlsx
@@ -11,14 +11,15 @@
     <sheet name="Shipped code review" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Evaluator comparison" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Migration path" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Framework coverage" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Competitive matrix" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Deterministic vs LLM" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Acceptance tests" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="KPIs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Risk register" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Roadmap" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Evidence and sources" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Applied and verified" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Framework coverage" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Competitive matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Deterministic vs LLM" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Acceptance tests" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="KPIs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Risk register" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Roadmap" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Evidence and sources" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -362,7 +363,34 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="KPIs" displayName="KPIs" ref="A4:E15" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Determinism" displayName="Determinism" ref="A4:D14" headerRowCount="1">
+  <autoFilter ref="A4:D14"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Dimension"/>
+    <tableColumn id="2" name="Deterministic engine"/>
+    <tableColumn id="3" name="LLM in the path"/>
+    <tableColumn id="4" name="Which wins, and why"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Acceptance" displayName="Acceptance" ref="A4:E15" headerRowCount="1">
+  <autoFilter ref="A4:E15"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="#"/>
+    <tableColumn id="2" name="Test"/>
+    <tableColumn id="3" name="Expected invariant"/>
+    <tableColumn id="4" name="Result"/>
+    <tableColumn id="5" name="How it is verified"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="KPIs" displayName="KPIs" ref="A4:E15" headerRowCount="1">
   <autoFilter ref="A4:E15"/>
   <tableColumns count="5">
     <tableColumn id="1" name="KPI"/>
@@ -375,8 +403,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Bench" displayName="Bench" ref="A18:F24" headerRowCount="1">
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Bench" displayName="Bench" ref="A18:F24" headerRowCount="1">
   <autoFilter ref="A18:F24"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Operation"/>
@@ -390,8 +418,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Risks" displayName="Risks" ref="A4:H16" headerRowCount="1">
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Risks" displayName="Risks" ref="A4:H16" headerRowCount="1">
   <autoFilter ref="A4:H16"/>
   <tableColumns count="8">
     <tableColumn id="1" name="ID"/>
@@ -407,8 +435,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Roadmap" displayName="Roadmap" ref="A4:E15" headerRowCount="1">
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Roadmap" displayName="Roadmap" ref="A4:E15" headerRowCount="1">
   <autoFilter ref="A4:E15"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Phase"/>
@@ -421,8 +449,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Evidence" displayName="Evidence" ref="A4:D13" headerRowCount="1">
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Evidence" displayName="Evidence" ref="A4:D13" headerRowCount="1">
   <autoFilter ref="A4:D13"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Claim"/>
@@ -434,8 +462,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Modules" displayName="Modules" ref="A16:C27" headerRowCount="1">
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Modules" displayName="Modules" ref="A16:C27" headerRowCount="1">
   <autoFilter ref="A16:C27"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Layer"/>
@@ -446,8 +474,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Sources" displayName="Sources" ref="A30:B51" headerRowCount="1">
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Sources" displayName="Sources" ref="A30:B51" headerRowCount="1">
   <autoFilter ref="A30:B51"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Source"/>
@@ -503,7 +531,33 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Coverage" displayName="Coverage" ref="A4:E38" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Applied" displayName="Applied" ref="A4:E11" headerRowCount="1">
+  <autoFilter ref="A4:E11"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Change"/>
+    <tableColumn id="3" name="Where"/>
+    <tableColumn id="4" name="What it does"/>
+    <tableColumn id="5" name="Evidence"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Verify" displayName="Verify" ref="A14:C21" headerRowCount="1">
+  <autoFilter ref="A14:C21"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Check"/>
+    <tableColumn id="2" name="Result"/>
+    <tableColumn id="3" name="Note"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Coverage" displayName="Coverage" ref="A4:E38" headerRowCount="1">
   <autoFilter ref="A4:E38"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section"/>
@@ -516,8 +570,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Capability" displayName="Capability" ref="A4:M24" headerRowCount="1">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Capability" displayName="Capability" ref="A4:M24" headerRowCount="1">
   <autoFilter ref="A4:M24"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Capability"/>
@@ -538,41 +592,14 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Products" displayName="Products" ref="A27:D38" headerRowCount="1">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Products" displayName="Products" ref="A27:D38" headerRowCount="1">
   <autoFilter ref="A27:D38"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Product"/>
     <tableColumn id="2" name="Category"/>
     <tableColumn id="3" name="Type"/>
     <tableColumn id="4" name="What it is known for"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Determinism" displayName="Determinism" ref="A4:D14" headerRowCount="1">
-  <autoFilter ref="A4:D14"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="Dimension"/>
-    <tableColumn id="2" name="Deterministic engine"/>
-    <tableColumn id="3" name="LLM in the path"/>
-    <tableColumn id="4" name="Which wins, and why"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Acceptance" displayName="Acceptance" ref="A4:E15" headerRowCount="1">
-  <autoFilter ref="A4:E15"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="#"/>
-    <tableColumn id="2" name="Test"/>
-    <tableColumn id="3" name="Expected invariant"/>
-    <tableColumn id="4" name="Result"/>
-    <tableColumn id="5" name="How it is verified"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
@@ -1173,6 +1200,566 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Engineering KPIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>The framework's Section 14 targets against measured values. Latency figures are engine CPU only; endpoint latency adds database and network time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Station creation p95</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>&lt; 800 ms</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>0.105 ms (engine CPU)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>0.01% of budget consumed by compute; remainder available for D1 round trips</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Evaluation API p95 (deterministic)</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>&lt; 300 ms</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>0.356 ms (engine CPU)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>0.12% of budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Next question client transition p95</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>&lt; 150 ms</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>0 ms engine cost</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Order is precompiled and persisted; no engine work occurs on transition</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Upload acknowledgement p95</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>&lt; 1.5 s</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>32.1 ms for a 10 KB file</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>2.1% of budget; supports synchronous ingestion without a queue</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Admin candidate list p95</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>&lt; 800 ms</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Not measured (I/O bound)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>By design</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Keyset-paginated index ix_candidate_review_queue; requires a live D1 to measure</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Extraction candidate precision after review</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>&gt;= 90%</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Not yet measurable</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Requires a labelled corpus of real OSCE files. Instrumentation is in place</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Incorrect examiner auto-merge</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>0 tolerated</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Structural: automatic match requires exact canonical or alias. Verified against 4 adversarial pairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Station creation failure rate</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>&lt; 0.5%</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>0 in 350 compilations</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>All failures are typed and deliberate (no published examiner, insufficient questions)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Duplicate publish incidents</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>UNIQUE (fingerprint) plus plan-level deduplication</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Dynamic publication delay after reviewer action</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>&lt; 5 s</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Not measured (I/O bound)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>By design</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Plan/apply split keeps the transaction to a single round trip</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Browser console core errors</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>Out of scope</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>This deliverable is the engine, not the client</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Benchmark detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Corpus</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>p50 (ms)</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>p95 (ms)</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>p99 (ms)</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Samples</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Station compilation (random, 5 questions)</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>7,200 questions / 19,800 occurrences</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Answer evaluation (6 key points, mixed languages)</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>5 representative answers</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Question dedup lookup</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>5,000-question corpus</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>1.437</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>1.992</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Examiner resolution (realistic names)</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>3,000 examiners, 970 blocking buckets</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>2.057</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>6.977</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Examiner resolution (degenerate blocking)</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>3,000 examiners, 4 buckets</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>17.539</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>20.252</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>24.774</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Ingestion of a 10 KB recall file</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>40 examiner blocks, 120 questions</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>32.103</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>34.689</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>The degenerate-blocking row is measured deliberately. It is the failure mode where every examiner name shares one phonetic skeleton, and it exists in the benchmark so the cost of that failure is known in advance rather than discovered in production.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A17:E17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1758,7 +2345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2132,7 +2719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3102,7 +3689,7 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -3112,17 +3699,17 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>question_occurrences has no fingerprint column and no UNIQUE constraint, and observation_count is a stored column on examiner_cases / examiner_questions.</t>
+          <t>observation_count, first_observed_year and last_observed_year on examiner_cases and examiner_questions are declared but never written by any code path. The publish route inserts the link rows with INSERT OR IGNORE and no count. Separately, question_occurrences has no fingerprint and no UNIQUE constraint, so a re-processed document creates duplicate evidence rows.</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>The framework's acceptance test 4 - re-publishing a document must not inflate observation counts - is not enforced anywhere in the schema. If counts are incremented rather than recomputed, a reprocess silently doubles every 'asked N times' figure, which is the number the whole product is built on.</t>
+          <t>The historical-frequency signal the entire product rests on does not exist. Every row holds the DEFAULT 0, so 'this examiner asked this question five times' is always zero, and the framework's station selection score - which weights normalised historical frequency at 0.45 - is multiplying a constant zero. This was verified by grepping every reference to the column across the codebase: two DDL declarations, no reads, no writes.</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>Add a deterministic fingerprint column with a UNIQUE index, and recompute counts from occurrences rather than incrementing. Migration 0005 plus the publisher change.</t>
+          <t>Recompute counts from approved occurrences at publish time, and add a deterministic occurrence fingerprint with a unique index so a replay is a no-op. Migration 0005 plus the publisher change; both applied and verified.</t>
         </is>
       </c>
     </row>
@@ -4170,6 +4757,417 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Applied to the shipped app, and verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Changes made to osce-app/ in this session, and what was actually run against them. No Cloudflare resource was created, listed or modified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Where</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>What it does</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Evaluator replaced</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>lib/evaluation.ts + lib/engine/</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Whole-token matching through the controlled vocabulary. Public API, input shape and stored key-point format unchanged, so no route and no migration was touched.</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>13 new regression tests; the original contract test still passes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Resubmission blocked</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>app/api/evaluate + app/api/exam-sessions/answers</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>INSERT ... ON CONFLICT DO NOTHING; returns 409 ALREADY_ANSWERED when a question is already answered.</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Verified by typecheck and build; needs acceptance row 12 against a live deployment</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Counts derived, occurrences fingerprinted</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>publish route + drizzle/0005</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Deterministic fingerprint with a partial unique index; observation counts and year bounds recomputed from approved occurrences after each publish, never incremented.</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Additive migration; acceptance rows 8 and 9 verify it on a live database</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Constant-time admin token compare</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>lib/knowledge/db.ts</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Length checked separately, then every byte examined regardless of where a mismatch occurs.</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Typecheck and lint clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Confidence stored as a number</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>lib/knowledge/db.ts + evaluate route</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Fresh databases declare the column REAL. The existing production database keeps TEXT affinity, so aggregates there need CAST(confidence AS REAL).</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Documented in the runbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Self-score derived server-side</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>app/api/exam-sessions/answers</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Score computed from the declared correctness rather than trusting a client-supplied number.</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Typecheck clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>ENV</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Node engines corrected</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>package.json</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>pdfjs-dist@6 calls Promise.try, which needs Node &gt;= 23. The declared range permitted Node 22, where both PDF tests fail and PDF upload breaks. Now &gt;=24.0.0.</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Reproduced: Promise.try is undefined on Node 22.22.2; both PDF tests fail identically before any other change</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Verification run</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>tsc --noEmit</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>clean</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>verified in session</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>eslint</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>clean</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>verified in session</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Test suite</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>20 of 22 passing</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>the 2 failures are the PDF tests, which need Node &gt;= 24; they fail identically on the unmodified baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>New evaluator tests</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>13 of 13 passing</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>verified in session</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>vinext build (build:cloudflare)</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>succeeds, 9 routes</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>verified in session</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>wrangler deploy --dry-run</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>succeeds; 2486 KiB upload, 748 KiB gzipped; DB, DOCUMENTS and ASSETS bindings resolve</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>verified in session</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Cloudflare deployment</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>not attempted</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>no credentials, no wrangler auth, MCP connector unauthorized, account verification outstanding, owner had halted the cutover</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Cloudflare deployment was not attempted and could not be: the session had no Cloudflare credentials, no wrangler authentication and an unauthorized MCP connector, and the handoff brief records that the owner halted the cutover pending account verification. See osce-app/DEPLOYMENT_RUNBOOK.md for the remaining sequence.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A13:E13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5159,7 +6157,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6889,7 +7887,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7180,7 +8178,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7544,564 +8542,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Engineering KPIs</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>The framework's Section 14 targets against measured values. Latency figures are engine CPU only; endpoint latency adds database and network time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Measured</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Station creation p95</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>&lt; 800 ms</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>0.105 ms (engine CPU)</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>0.01% of budget consumed by compute; remainder available for D1 round trips</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Evaluation API p95 (deterministic)</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>&lt; 300 ms</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>0.356 ms (engine CPU)</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>0.12% of budget</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Next question client transition p95</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>&lt; 150 ms</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>0 ms engine cost</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Order is precompiled and persisted; no engine work occurs on transition</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Upload acknowledgement p95</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>&lt; 1.5 s</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>32.1 ms for a 10 KB file</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>2.1% of budget; supports synchronous ingestion without a queue</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Admin candidate list p95</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>&lt; 800 ms</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Not measured (I/O bound)</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>By design</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Keyset-paginated index ix_candidate_review_queue; requires a live D1 to measure</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Extraction candidate precision after review</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>&gt;= 90%</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Not yet measurable</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>Requires a labelled corpus of real OSCE files. Instrumentation is in place</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Incorrect examiner auto-merge</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>0 tolerated</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Structural: automatic match requires exact canonical or alias. Verified against 4 adversarial pairs</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Station creation failure rate</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>&lt; 0.5%</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>0 in 350 compilations</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>All failures are typed and deliberate (no published examiner, insufficient questions)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Duplicate publish incidents</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>UNIQUE (fingerprint) plus plan-level deduplication</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Dynamic publication delay after reviewer action</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>&lt; 5 s</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Not measured (I/O bound)</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>By design</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>Plan/apply split keeps the transaction to a single round trip</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Browser console core errors</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>Out of scope</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>This deliverable is the engine, not the client</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Benchmark detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Operation</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Corpus</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>p50 (ms)</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>p95 (ms)</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>p99 (ms)</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>Samples</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>Station compilation (random, 5 questions)</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>7,200 questions / 19,800 occurrences</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Answer evaluation (6 key points, mixed languages)</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>5 representative answers</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="D20" s="15" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="F20" s="15" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>Question dedup lookup</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>5,000-question corpus</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>1.437</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>1.992</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Examiner resolution (realistic names)</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>3,000 examiners, 970 blocking buckets</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="n">
-        <v>2.057</v>
-      </c>
-      <c r="D22" s="15" t="n">
-        <v>6.977</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="F22" s="15" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>Examiner resolution (degenerate blocking)</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>3,000 examiners, 4 buckets</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>17.539</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>20.252</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>24.774</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Ingestion of a 10 KB recall file</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>40 examiner blocks, 120 questions</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="D24" s="15" t="n">
-        <v>32.103</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>34.689</v>
-      </c>
-      <c r="F24" s="15" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>The degenerate-blocking row is measured deliberately. It is the failure mode where every examiner name shares one phonetic skeleton, and it exists in the benchmark so the cost of that failure is known in advance rather than discovered in production.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A17:E17"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="2">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
-</worksheet>
 </file>